--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.78768389888692</v>
+        <v>5.652998633569124</v>
       </c>
       <c r="D2" t="n">
-        <v>36.19487940108993</v>
+        <v>5.881667902677114</v>
       </c>
       <c r="E2" t="n">
-        <v>8.69617210514595</v>
+        <v>1.413127967086217</v>
       </c>
       <c r="F2" t="n">
-        <v>9.422542888038187</v>
+        <v>1.531163219306205</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>24.0198222174131</v>
+        <v>3.903221110329629</v>
       </c>
       <c r="D3" t="n">
-        <v>23.05796207898229</v>
+        <v>3.746918837834622</v>
       </c>
       <c r="E3" t="n">
-        <v>8.69617210514595</v>
+        <v>1.413127967086217</v>
       </c>
       <c r="F3" t="n">
-        <v>9.422542888038187</v>
+        <v>1.531163219306205</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.89746297812816</v>
+        <v>2.745837733945826</v>
       </c>
       <c r="D4" t="n">
-        <v>16.15314807598915</v>
+        <v>2.624886562348236</v>
       </c>
       <c r="E4" t="n">
-        <v>8.69617210514595</v>
+        <v>1.413127967086217</v>
       </c>
       <c r="F4" t="n">
-        <v>9.422542888038187</v>
+        <v>1.531163219306205</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.94924126592296</v>
+        <v>5.354251705712481</v>
       </c>
       <c r="D5" t="n">
-        <v>33.39445137617999</v>
+        <v>5.426598348629248</v>
       </c>
       <c r="E5" t="n">
-        <v>8.69617210514595</v>
+        <v>1.413127967086217</v>
       </c>
       <c r="F5" t="n">
-        <v>9.422542888038187</v>
+        <v>1.531163219306205</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>34.51467101652135</v>
+        <v>5.608634040184721</v>
       </c>
       <c r="D6" t="n">
-        <v>32.33939784530178</v>
+        <v>5.25515214986154</v>
       </c>
       <c r="E6" t="n">
-        <v>8.69617210514595</v>
+        <v>1.413127967086217</v>
       </c>
       <c r="F6" t="n">
-        <v>9.422542888038187</v>
+        <v>1.531163219306205</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.00180543018717</v>
+        <v>2.112793382405414</v>
       </c>
       <c r="D7" t="n">
-        <v>10.80014288885814</v>
+        <v>1.755023219439448</v>
       </c>
       <c r="E7" t="n">
-        <v>8.69617210514595</v>
+        <v>1.413127967086217</v>
       </c>
       <c r="F7" t="n">
-        <v>9.422542888038187</v>
+        <v>1.531163219306205</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
